--- a/Config/Excel/login.xlsx
+++ b/Config/Excel/login.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19DC33E-7CA5-4F6A-9914-69A8F8A4922A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27E1C23-92FC-477F-BC61-A18722FD047B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
@@ -52,13 +52,33 @@
   </si>
   <si>
     <t>结束游戏</t>
+  </si>
+  <si>
+    <t>sys_910001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sys_910002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sys_910003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sys_910004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,6 +88,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -96,11 +124,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -410,8 +441,8 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
@@ -432,8 +463,8 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1">
-        <v>910001</v>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D5" s="1">
         <v>999</v>
@@ -446,8 +477,8 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="1">
-        <v>910002</v>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="1">
         <v>998</v>
@@ -460,8 +491,8 @@
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1">
-        <v>910003</v>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D7" s="1">
         <v>997</v>
@@ -474,8 +505,8 @@
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1">
-        <v>910004</v>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D8" s="1">
         <v>996</v>
